--- a/results/Int All Data -0.5/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.5/Linea_fi_all.xlsx
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.02095032397408205 +/- 0.003403677584318233</t>
+          <t>0.02091946929959887 +/- 0.0033454208376253788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-9.25640234495706e-05 +/- 0.0010330557878915738</t>
+          <t>-6.17093489663878e-05 +/- 0.0010580949212886128</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1571,72 +1571,72 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
+          <t>0.000617093489663667 +/- 0.0004975166768465677</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.010274606602900327 +/- 0.002756446859980116</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.0005862388151805176 +/- 0.0009800913405904738</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.0005862388151805176 +/- 0.0009800913405904738</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.00987349583461894 +/- 0.0024837533844490243</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>0.009935205183585294 +/- 0.0022241062994063565</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.014810243751928387 +/- 0.002413774417230236</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.0019129898179574111 +/- 0.0012631588701301126</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>-0.001635297747608766 +/- 0.0009859022097297378</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0.0014810243751928408 +/- 0.0010759392640643435</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>0.4092564023449553 +/- 0.007934152206053301</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0.004504782474544888 +/- 0.001852308672607677</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>0.2584078987966677 +/- 0.00812158099153986</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
           <t>0.0005862388151804843 +/- 0.00042418164408724793</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.010274606602900327 +/- 0.002756446859980116</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.0005862388151805176 +/- 0.0009800913405904738</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.0005862388151805176 +/- 0.0009800913405904738</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.00987349583461894 +/- 0.0024837533844490243</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.009935205183585294 +/- 0.0022241062994063565</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.014810243751928387 +/- 0.002413774417230236</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.0019129898179574111 +/- 0.0012631588701301126</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>-0.001635297747608766 +/- 0.0009859022097297378</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0014810243751928408 +/- 0.0010759392640643435</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.4092564023449553 +/- 0.007934152206053301</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>0.004504782474544888 +/- 0.001852308672607677</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>0.2584078987966677 +/- 0.00812158099153986</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>0.000617093489663667 +/- 0.0004975166768465677</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0001784121320249299 +/- 0.00038079834894039753</t>
+          <t>0.00014867677668743972 +/- 0.0003819575551193862</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.02010110020814747 +/- 0.0025308263848888815</t>
+          <t>0.02013083556348496 +/- 0.0025992510765982914</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>0.0010107015457788472 +/- 0.0005974955779500986</t>
+          <t>0.0009809750297265275 +/- 0.0006242568370986796</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.00613729832331541 +/- 0.0018018387682249989</t>
+          <t>-0.0061689338816830145 +/- 0.0018131894819243292</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0016450490351154756 +/- 0.00036893083801618954</t>
+          <t>-0.0016134134767478603 +/- 0.00035931087287572363</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.02863018032268271 +/- 0.0026211735383077886</t>
+          <t>-0.028598544764315094 +/- 0.0026362121677949556</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.007620237351655157 +/- 0.0019662806044593757</t>
+          <t>-0.00758900687070575 +/- 0.001985286080613732</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-0.0007183478000598598 +/- 0.0019772696276460565</t>
+          <t>-0.0006884166417240323 +/- 0.0019991235533668343</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
